--- a/WEIGHTING SEDERHANA.xlsx
+++ b/WEIGHTING SEDERHANA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMESTER 4\TEKSAM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C175C63-2148-48A8-86E6-4123D89B7E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B273E91C-E792-4AF7-9FF6-27423299901B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FF2F6E9-C33E-4821-B789-0606799DD27C}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3FF2F6E9-C33E-4821-B789-0606799DD27C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>JENIS KELAMIN</t>
   </si>
@@ -61,12 +61,60 @@
   </si>
   <si>
     <t>BOBOT</t>
+  </si>
+  <si>
+    <t>HITUNG WEIGHTING</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>SIGMA Wi</t>
+  </si>
+  <si>
+    <t>SIGMA WiYi</t>
+  </si>
+  <si>
+    <t>Weight Sederhana</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -96,8 +144,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,10 +464,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B234EAC7-BB64-4379-B2F1-3A00262E8DC6}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
@@ -505,7 +557,207 @@
         <v>1.7970000000000002</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <f>4*F2+13*F3</f>
+        <v>17.835000000000001</v>
+      </c>
+      <c r="C9">
+        <f>(9*F2)+(19*F3)</f>
+        <v>28.003</v>
+      </c>
+      <c r="D9" s="2">
+        <f>B9/C9</f>
+        <v>0.63689604685212298</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <f>5*F2+14*F3</f>
+        <v>19.632000000000001</v>
+      </c>
+      <c r="C10">
+        <v>28.003</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" ref="D10:D21" si="0">B10/C10</f>
+        <v>0.70106774274184913</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <f>0*F2+6*F3</f>
+        <v>7.0980000000000008</v>
+      </c>
+      <c r="C11">
+        <v>28.003</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.25347284219547911</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <f>5*F2+11*F3</f>
+        <v>16.082999999999998</v>
+      </c>
+      <c r="C12">
+        <v>28.003</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.57433132164410949</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <f>4*F2+11*F3</f>
+        <v>15.468999999999999</v>
+      </c>
+      <c r="C13">
+        <v>28.003</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.55240509945362992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <f>6*F2+15*F3</f>
+        <v>21.429000000000002</v>
+      </c>
+      <c r="C14">
+        <v>28.003</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.76523943863157529</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <f>7*F2+7*F3</f>
+        <v>12.579000000000001</v>
+      </c>
+      <c r="C15">
+        <v>28.003</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.44920187122808275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <f>6*F2+13*F3</f>
+        <v>19.063000000000002</v>
+      </c>
+      <c r="C16">
+        <v>28.003</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.68074849123308223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <f>8*F2+14*F3</f>
+        <v>21.474</v>
+      </c>
+      <c r="C17">
+        <v>28.003</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.76684640931328785</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <f>8*F2+15*F3</f>
+        <v>22.657</v>
+      </c>
+      <c r="C18">
+        <v>28.003</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.80909188301253432</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <f>6*F2+15*F3</f>
+        <v>21.429000000000002</v>
+      </c>
+      <c r="C19">
+        <v>28.003</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.76523943863157529</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:E7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>